--- a/fixtures/mis/FIXTURE_ONLY/salad-days/FIXTURE_ONLY-salad-days-below-plan.xlsx
+++ b/fixtures/mis/FIXTURE_ONLY/salad-days/FIXTURE_ONLY-salad-days-below-plan.xlsx
@@ -445,7 +445,7 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="C2">
         <v>2.8</v>
@@ -459,7 +459,7 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C3">
         <v>46</v>
@@ -473,7 +473,7 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="C4">
         <v>1.7</v>
@@ -487,7 +487,7 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>-0.2</v>
+        <v>-0.45</v>
       </c>
       <c r="C5">
         <v>0.3</v>
@@ -501,7 +501,7 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="D6">
         <v>1.6</v>
@@ -512,7 +512,7 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>0.35</v>
+        <v>0.48</v>
       </c>
       <c r="C7">
         <v>0.2</v>
@@ -540,7 +540,7 @@
         <v>11</v>
       </c>
       <c r="B9">
-        <v>95000</v>
+        <v>88000</v>
       </c>
       <c r="C9">
         <v>110000</v>
